--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT TRANSMISSÃO - 14_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT TRANSMISSÃO - 14_01.xlsx
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>7895099121483</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT TRANSMISSÃO - 14_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT TRANSMISSÃO - 14_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,17 +444,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KIT TRASMISSAO W-MAX CB300 2009 A 2015 5876880034</t>
+          <t>KIT TRASMISSAO WURTH CB300 2009 A 2015 5876880034</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>360</t>
         </is>
       </c>
     </row>
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,7 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -720,7 +664,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX XR300 2009 5986880030</t>
+          <t>KIT TRANSMISSAO WURTH XRE300 2009 5986880030</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -728,7 +672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -741,17 +684,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX XR300 2009 5986880029</t>
+          <t>KIT TRANSMISSAO WURTH XRE300 2009 5986880029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>180</t>
         </is>
       </c>
     </row>
@@ -766,7 +704,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX NXR150 BROS 2003 A 2014 5986880017</t>
+          <t>KIT TRANSMISSAO WURTH NXR150 BROS 2003 A 2014 5986880017</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -774,7 +712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -795,11 +732,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -820,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -845,7 +772,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -866,7 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -879,17 +804,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX TITAN160/ FAN160 2015 5986880006</t>
+          <t>KIT TRANSMISSAO WURTH TITAN160/ FAN160 2015 5986880006</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>220</t>
         </is>
       </c>
     </row>
@@ -904,7 +824,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO  W-MAX FAN 125 2009 5986880024</t>
+          <t>KIT TRANSMISSAO  WURTH FAN 125 2009 5986880024</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -912,7 +832,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -933,7 +852,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -954,7 +872,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -975,7 +892,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -996,7 +912,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1017,7 +932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1038,7 +952,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1051,7 +964,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX FACTOR 2020 5986880120</t>
+          <t>KIT TRANSMISSAO WURTH FACTOR 2020 5986880120</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1059,7 +972,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1080,7 +992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1101,7 +1012,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1114,7 +1024,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX FAZER NOVA 2018 5986880115</t>
+          <t>KIT TRANSMISSAO WURTH FAZER NOVA 2018 5986880115</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1122,7 +1032,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1143,7 +1052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1164,7 +1072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,7 +1084,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX FAZER250 2005 A 2017</t>
+          <t>KIT TRANSMISSAO WURTH FAZER250 2005 A 2017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1185,7 +1092,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1206,7 +1112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1227,7 +1132,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1248,7 +1152,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1269,7 +1172,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1290,7 +1192,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1311,7 +1212,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1332,7 +1232,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1345,7 +1244,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO IRON NXR150 122787</t>
+          <t>KIT TRANSMISSAO IRON BROS NXR150 122787</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1353,7 +1252,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1366,7 +1264,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO IRON NXR160/ XRE190 026823</t>
+          <t>KIT TRANSMISSAO IRON BROS NXR160/ XRE190 026823</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1374,7 +1272,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1387,7 +1284,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO COFAP NXR160/ XRE190 TMCC410014</t>
+          <t>KIT TRANSMISSAO COFAP BROS NXR160/ XRE190 TMCC410014</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1395,7 +1292,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1408,7 +1304,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSA W-MAX NXR160 2014 5986880020</t>
+          <t>KIT TRANSMISSA WURTH BROS NXR160 2014 5986880020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1416,7 +1312,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1429,7 +1324,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO RIFFEL NXR160 2008 001-UNI-04900</t>
+          <t>KIT TRANSMISSAO UNIK BROS NXR160 2008 001-UNI-04900</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1437,7 +1332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1450,7 +1344,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX NXR150 2003 A 2014 5986880017</t>
+          <t>KIT TRANSMISSAO BROS WURTH BROS NXR150 2003 A 2014 5986880017</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1458,7 +1352,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1471,7 +1364,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO C/ ANEL VEDACAO W-MAX NXR150 2004 A 2014 5986880018</t>
+          <t>KIT TRANSMISSAO C/ ANEL VEDACAO WURTH BROS NXR150 2004 A 2014 5986880018</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1479,7 +1372,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1492,7 +1384,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO RIFFEL NXR150 2006 A 2015 71884</t>
+          <t>KIT TRANSMISSAO RIFFEL BROS NXR150 2006 A 2015 71884</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1500,7 +1392,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1513,7 +1404,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO IRON PREMIER NXR150 ESD 2012 17149</t>
+          <t>KIT TRANSMISSAO IRON PREMIER BROS NXR150 ESD 2012 17149</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1521,7 +1412,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1534,7 +1424,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO WURTH NXR150 2003 A 2014 8500706</t>
+          <t>KIT TRANSMISSAO WURTH BROS NXR150 2003 A 2014 8500706</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1542,7 +1432,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1555,17 +1444,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO SMARTFOX NXR150 2003 A 2015 41300-DF1-BR03</t>
+          <t>KIT TRANSMISSAO SMARTFOX BROS NXR150 2003 A 2015 41300-DF1-BR03</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>215</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1464,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX POP110 2016 5986880037</t>
+          <t>KIT TRANSMISSAO WURTH POP110 2016 5986880037</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1588,7 +1472,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1601,7 +1484,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX BIZ125/ POP100 2006 5986880036</t>
+          <t>KIT TRANSMISSAO WURTH BIZ125/ POP100 2006 5986880036</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1609,7 +1492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1622,7 +1504,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO RIFFEL BIZ110 2016 001-UNI-06600</t>
+          <t>KIT TRANSMISSAO UNIK BIZ110 2016 001-UNI-06600</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1630,7 +1512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1651,7 +1532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1672,7 +1552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1685,7 +1564,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO W-MAX XTZ250 LANDER 2009 5986880109</t>
+          <t>KIT TRANSMISSAO WURTH XTZ250 LANDER 2009 5986880109</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1693,7 +1572,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1714,11 +1592,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1739,11 +1612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1764,7 +1632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1785,11 +1652,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1810,11 +1672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1835,11 +1692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1860,7 +1712,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1881,7 +1732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1902,7 +1752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1923,7 +1772,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1944,11 +1792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1969,7 +1812,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1986,11 +1828,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2011,7 +1848,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2024,7 +1860,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KIT TRANSMISSAO IRON NXR150 122787</t>
+          <t>KIT TRANSMISSAO IRON  BROS NXR150 122787</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2032,7 +1868,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2053,7 +1888,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2074,7 +1908,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2095,7 +1928,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2116,7 +1948,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2137,7 +1968,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2158,7 +1988,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2179,7 +2008,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2200,7 +2028,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2221,7 +2048,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2242,7 +2068,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
